--- a/executivos/thozen-electra/Thozen - Electra_COMPOSIÇÕES2.xlsx
+++ b/executivos/thozen-electra/Thozen - Electra_COMPOSIÇÕES2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Drives compartilhados\03 CTN Projetos\2. Projetos em Andamento\_Executivo_IA\thozen-electra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81BEA83-0EA7-4F94-BEDE-297537ACFCF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A648B68-A7FD-4411-AC06-F70575AC1C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E6DAAFF2-9163-4450-B133-7FD4778E9B32}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11569" uniqueCount="1732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11569" uniqueCount="1731">
   <si>
     <t>&lt;codigo&gt;</t>
   </si>
@@ -5255,9 +5255,6 @@
   </si>
   <si>
     <t>(Todos)</t>
-  </si>
-  <si>
-    <t>reboco externo</t>
   </si>
 </sst>
 </file>
@@ -56296,15 +56293,15 @@
       </c>
       <c r="M2" t="b">
         <f>IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;1,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),101,100)),G2)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="b">
         <f>IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;2,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),201,100)),G2)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="b">
         <f>IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;3,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),301,100)),G2)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <f>L2*M2*N2*O2</f>
@@ -56324,7 +56321,7 @@
         <v>1720</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>1731</v>
+        <v>149</v>
       </c>
       <c r="C3" s="33"/>
       <c r="D3" s="28" t="str">
@@ -56359,11 +56356,11 @@
       </c>
       <c r="N3" t="b">
         <f t="shared" ref="N3:N66" si="2">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;2,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),201,100)),G3)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="b">
         <f t="shared" ref="O3:O66" si="3">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;3,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),301,100)),G3)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <f t="shared" ref="P3:P66" si="4">L3*M3*N3*O3</f>
@@ -56410,11 +56407,11 @@
       </c>
       <c r="N4" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <f t="shared" si="4"/>
@@ -56473,11 +56470,11 @@
       </c>
       <c r="N5" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <f t="shared" si="4"/>
@@ -56495,23 +56492,23 @@
     <row r="6" spans="1:18" ht="19.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="27" cm="1">
         <f t="array" ref="A6">IFERROR(_xlfn._xlws.FILTER(F2:F538,R2:R538),"Nenhum resultado")</f>
-        <v>4983</v>
+        <v>90528</v>
       </c>
       <c r="B6" s="31" t="str" cm="1">
         <f t="array" ref="B6">IFERROR(_xlfn._xlws.FILTER(G2:G538,R2:R538),"")</f>
-        <v xml:space="preserve"> Mão de obra para execução de reboco externo, inclui chapisco</v>
+        <v>Brise com palhetas verticais</v>
       </c>
       <c r="C6" s="27" t="str" cm="1">
         <f t="array" ref="C6">IFERROR(_xlfn._xlws.FILTER(H2:H538,R2:R538),"")</f>
-        <v>m2</v>
+        <v>m²</v>
       </c>
       <c r="D6" s="26" t="str" cm="1">
         <f t="array" ref="D6">IFERROR(_xlfn._xlws.FILTER(I2:I538,R2:R538),"")</f>
-        <v>REVESTIMENTOS E ACABAMENTOS EM FACHADA</v>
-      </c>
-      <c r="E6" s="26" cm="1">
+        <v>ESQUADRIAS</v>
+      </c>
+      <c r="E6" s="26" t="str" cm="1">
         <f t="array" ref="E6">IFERROR(_xlfn._xlws.FILTER(J2:J538,R2:R538),"")</f>
-        <v>0</v>
+        <v>Geral</v>
       </c>
       <c r="F6">
         <v>90553</v>
@@ -56541,11 +56538,11 @@
       </c>
       <c r="N6" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <f t="shared" si="4"/>
@@ -56594,11 +56591,11 @@
       </c>
       <c r="N7" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <f t="shared" si="4"/>
@@ -56644,11 +56641,11 @@
       </c>
       <c r="N8" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <f t="shared" si="4"/>
@@ -56697,11 +56694,11 @@
       </c>
       <c r="N9" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <f t="shared" si="4"/>
@@ -56716,7 +56713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="37.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:18" ht="19.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="27"/>
       <c r="B10" s="31"/>
       <c r="C10" s="27"/>
@@ -56747,11 +56744,11 @@
       </c>
       <c r="N10" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10">
         <f t="shared" si="4"/>
@@ -56797,11 +56794,11 @@
       </c>
       <c r="N11" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11">
         <f t="shared" si="4"/>
@@ -56846,15 +56843,15 @@
       </c>
       <c r="M12" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <f t="shared" si="4"/>
@@ -56900,11 +56897,11 @@
       </c>
       <c r="N13" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13">
         <f t="shared" si="4"/>
@@ -56950,11 +56947,11 @@
       </c>
       <c r="N14" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14">
         <f t="shared" si="4"/>
@@ -56999,15 +56996,15 @@
       </c>
       <c r="M15" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15">
         <f t="shared" si="4"/>
@@ -57052,15 +57049,15 @@
       </c>
       <c r="M16" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16">
         <f t="shared" si="4"/>
@@ -57106,11 +57103,11 @@
       </c>
       <c r="N17" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17">
         <f t="shared" si="4"/>
@@ -57155,15 +57152,15 @@
       </c>
       <c r="M18" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18">
         <f t="shared" si="4"/>
@@ -57212,11 +57209,11 @@
       </c>
       <c r="N19" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19">
         <f t="shared" si="4"/>
@@ -57262,11 +57259,11 @@
       </c>
       <c r="N20" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20">
         <f t="shared" si="4"/>
@@ -57312,11 +57309,11 @@
       </c>
       <c r="N21" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21">
         <f t="shared" si="4"/>
@@ -57362,11 +57359,11 @@
       </c>
       <c r="N22" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22">
         <f t="shared" si="4"/>
@@ -57408,15 +57405,15 @@
       </c>
       <c r="M23" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23">
         <f t="shared" si="4"/>
@@ -57458,15 +57455,15 @@
       </c>
       <c r="M24" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24">
         <f t="shared" si="4"/>
@@ -57515,11 +57512,11 @@
       </c>
       <c r="N25" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25">
         <f t="shared" si="4"/>
@@ -57561,15 +57558,15 @@
       </c>
       <c r="M26" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26">
         <f t="shared" si="4"/>
@@ -57614,15 +57611,15 @@
       </c>
       <c r="M27" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27">
         <f t="shared" si="4"/>
@@ -57671,11 +57668,11 @@
       </c>
       <c r="N28" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28">
         <f t="shared" si="4"/>
@@ -57716,11 +57713,11 @@
       </c>
       <c r="L29" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="b">
         <f t="shared" si="2"/>
@@ -57732,7 +57729,7 @@
       </c>
       <c r="P29">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="b">
         <f t="shared" si="5"/>
@@ -57740,7 +57737,7 @@
       </c>
       <c r="R29">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="19.5" x14ac:dyDescent="0.55000000000000004">
@@ -57774,11 +57771,11 @@
       </c>
       <c r="N30" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30">
         <f t="shared" si="4"/>
@@ -57823,15 +57820,15 @@
       </c>
       <c r="M31" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P31">
         <f t="shared" si="4"/>
@@ -57876,15 +57873,15 @@
       </c>
       <c r="M32" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32">
         <f t="shared" si="4"/>
@@ -57929,15 +57926,15 @@
       </c>
       <c r="M33" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33">
         <f t="shared" si="4"/>
@@ -57986,11 +57983,11 @@
       </c>
       <c r="N34" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34">
         <f t="shared" si="4"/>
@@ -58032,15 +58029,15 @@
       </c>
       <c r="M35" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P35">
         <f t="shared" si="4"/>
@@ -58086,11 +58083,11 @@
       </c>
       <c r="N36" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P36">
         <f t="shared" si="4"/>
@@ -58136,11 +58133,11 @@
       </c>
       <c r="N37" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P37">
         <f t="shared" si="4"/>
@@ -58182,15 +58179,15 @@
       </c>
       <c r="M38" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P38">
         <f t="shared" si="4"/>
@@ -58232,15 +58229,15 @@
       </c>
       <c r="M39" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39">
         <f t="shared" si="4"/>
@@ -58282,15 +58279,15 @@
       </c>
       <c r="M40" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P40">
         <f t="shared" si="4"/>
@@ -58336,11 +58333,11 @@
       </c>
       <c r="N41" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P41">
         <f t="shared" si="4"/>
@@ -58386,11 +58383,11 @@
       </c>
       <c r="N42" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P42">
         <f t="shared" si="4"/>
@@ -58433,11 +58430,11 @@
       </c>
       <c r="N43" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P43">
         <f t="shared" si="4"/>
@@ -58480,11 +58477,11 @@
       </c>
       <c r="N44" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P44">
         <f t="shared" si="4"/>
@@ -58530,11 +58527,11 @@
       </c>
       <c r="N45" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P45">
         <f t="shared" si="4"/>
@@ -58580,11 +58577,11 @@
       </c>
       <c r="N46" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P46">
         <f t="shared" si="4"/>
@@ -58627,11 +58624,11 @@
       </c>
       <c r="N47" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P47">
         <f t="shared" si="4"/>
@@ -58674,11 +58671,11 @@
       </c>
       <c r="N48" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P48">
         <f t="shared" si="4"/>
@@ -58721,11 +58718,11 @@
       </c>
       <c r="N49" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P49">
         <f t="shared" si="4"/>
@@ -58767,15 +58764,15 @@
       </c>
       <c r="M50" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P50">
         <f t="shared" si="4"/>
@@ -58818,11 +58815,11 @@
       </c>
       <c r="N51" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P51">
         <f t="shared" si="4"/>
@@ -58861,15 +58858,15 @@
       </c>
       <c r="M52" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P52">
         <f t="shared" si="4"/>
@@ -58912,11 +58909,11 @@
       </c>
       <c r="N53" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53">
         <f t="shared" si="4"/>
@@ -58962,11 +58959,11 @@
       </c>
       <c r="N54" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P54">
         <f t="shared" si="4"/>
@@ -59005,15 +59002,15 @@
       </c>
       <c r="M55" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P55">
         <f t="shared" si="4"/>
@@ -59052,15 +59049,15 @@
       </c>
       <c r="M56" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P56">
         <f t="shared" si="4"/>
@@ -59099,15 +59096,15 @@
       </c>
       <c r="M57" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P57">
         <f t="shared" si="4"/>
@@ -59150,11 +59147,11 @@
       </c>
       <c r="N58" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P58">
         <f t="shared" si="4"/>
@@ -59200,11 +59197,11 @@
       </c>
       <c r="N59" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P59">
         <f t="shared" si="4"/>
@@ -59250,11 +59247,11 @@
       </c>
       <c r="N60" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P60">
         <f t="shared" si="4"/>
@@ -59296,15 +59293,15 @@
       </c>
       <c r="M61" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P61">
         <f t="shared" si="4"/>
@@ -59346,15 +59343,15 @@
       </c>
       <c r="M62" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P62">
         <f t="shared" si="4"/>
@@ -59393,15 +59390,15 @@
       </c>
       <c r="M63" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O63" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P63">
         <f t="shared" si="4"/>
@@ -59443,15 +59440,15 @@
       </c>
       <c r="M64" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P64">
         <f t="shared" si="4"/>
@@ -59493,15 +59490,15 @@
       </c>
       <c r="M65" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P65">
         <f t="shared" si="4"/>
@@ -59543,15 +59540,15 @@
       </c>
       <c r="M66" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N66" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O66" t="b">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P66">
         <f t="shared" si="4"/>
@@ -59597,11 +59594,11 @@
       </c>
       <c r="N67" t="b">
         <f t="shared" ref="N67:N130" si="9">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;2,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),201,100)),G67)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="b">
         <f t="shared" ref="O67:O130" si="10">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;3,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),301,100)),G67)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P67">
         <f t="shared" ref="P67:P130" si="11">L67*M67*N67*O67</f>
@@ -59647,11 +59644,11 @@
       </c>
       <c r="N68" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P68">
         <f t="shared" si="11"/>
@@ -59697,11 +59694,11 @@
       </c>
       <c r="N69" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P69">
         <f t="shared" si="11"/>
@@ -59747,11 +59744,11 @@
       </c>
       <c r="N70" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P70">
         <f t="shared" si="11"/>
@@ -59797,11 +59794,11 @@
       </c>
       <c r="N71" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P71">
         <f t="shared" si="11"/>
@@ -59847,11 +59844,11 @@
       </c>
       <c r="N72" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P72">
         <f t="shared" si="11"/>
@@ -59897,11 +59894,11 @@
       </c>
       <c r="N73" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P73">
         <f t="shared" si="11"/>
@@ -59943,15 +59940,15 @@
       </c>
       <c r="M74" t="b">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N74" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P74">
         <f t="shared" si="11"/>
@@ -59997,11 +59994,11 @@
       </c>
       <c r="N75" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P75">
         <f t="shared" si="11"/>
@@ -60047,11 +60044,11 @@
       </c>
       <c r="N76" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P76">
         <f t="shared" si="11"/>
@@ -60097,11 +60094,11 @@
       </c>
       <c r="N77" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P77">
         <f t="shared" si="11"/>
@@ -60147,11 +60144,11 @@
       </c>
       <c r="N78" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O78" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P78">
         <f t="shared" si="11"/>
@@ -60197,11 +60194,11 @@
       </c>
       <c r="N79" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P79">
         <f t="shared" si="11"/>
@@ -60247,11 +60244,11 @@
       </c>
       <c r="N80" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P80">
         <f t="shared" si="11"/>
@@ -60297,11 +60294,11 @@
       </c>
       <c r="N81" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P81">
         <f t="shared" si="11"/>
@@ -60347,11 +60344,11 @@
       </c>
       <c r="N82" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O82" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P82">
         <f t="shared" si="11"/>
@@ -60397,11 +60394,11 @@
       </c>
       <c r="N83" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P83">
         <f t="shared" si="11"/>
@@ -60447,11 +60444,11 @@
       </c>
       <c r="N84" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P84">
         <f t="shared" si="11"/>
@@ -60497,11 +60494,11 @@
       </c>
       <c r="N85" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P85">
         <f t="shared" si="11"/>
@@ -60547,11 +60544,11 @@
       </c>
       <c r="N86" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P86">
         <f t="shared" si="11"/>
@@ -60597,11 +60594,11 @@
       </c>
       <c r="N87" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P87">
         <f t="shared" si="11"/>
@@ -60647,11 +60644,11 @@
       </c>
       <c r="N88" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P88">
         <f t="shared" si="11"/>
@@ -60693,15 +60690,15 @@
       </c>
       <c r="M89" t="b">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N89" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P89">
         <f t="shared" si="11"/>
@@ -60747,11 +60744,11 @@
       </c>
       <c r="N90" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O90" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P90">
         <f t="shared" si="11"/>
@@ -60797,11 +60794,11 @@
       </c>
       <c r="N91" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P91">
         <f t="shared" si="11"/>
@@ -60843,15 +60840,15 @@
       </c>
       <c r="M92" t="b">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P92">
         <f t="shared" si="11"/>
@@ -60897,11 +60894,11 @@
       </c>
       <c r="N93" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P93">
         <f t="shared" si="11"/>
@@ -60947,11 +60944,11 @@
       </c>
       <c r="N94" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O94" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P94">
         <f t="shared" si="11"/>
@@ -60990,15 +60987,15 @@
       </c>
       <c r="M95" t="b">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N95" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O95" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P95">
         <f t="shared" si="11"/>
@@ -61040,15 +61037,15 @@
       </c>
       <c r="M96" t="b">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N96" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O96" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P96">
         <f t="shared" si="11"/>
@@ -61090,15 +61087,15 @@
       </c>
       <c r="M97" t="b">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N97" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O97" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P97">
         <f t="shared" si="11"/>
@@ -61140,15 +61137,15 @@
       </c>
       <c r="M98" t="b">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N98" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O98" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P98">
         <f t="shared" si="11"/>
@@ -61190,15 +61187,15 @@
       </c>
       <c r="M99" t="b">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N99" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O99" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P99">
         <f t="shared" si="11"/>
@@ -61240,15 +61237,15 @@
       </c>
       <c r="M100" t="b">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N100" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O100" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P100">
         <f t="shared" si="11"/>
@@ -61291,11 +61288,11 @@
       </c>
       <c r="N101" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O101" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P101">
         <f t="shared" si="11"/>
@@ -61341,11 +61338,11 @@
       </c>
       <c r="N102" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O102" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P102">
         <f t="shared" si="11"/>
@@ -61388,11 +61385,11 @@
       </c>
       <c r="N103" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O103" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P103">
         <f t="shared" si="11"/>
@@ -61435,11 +61432,11 @@
       </c>
       <c r="N104" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O104" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P104">
         <f t="shared" si="11"/>
@@ -61482,11 +61479,11 @@
       </c>
       <c r="N105" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O105" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P105">
         <f t="shared" si="11"/>
@@ -61529,11 +61526,11 @@
       </c>
       <c r="N106" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O106" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P106">
         <f t="shared" si="11"/>
@@ -61576,11 +61573,11 @@
       </c>
       <c r="N107" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O107" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P107">
         <f t="shared" si="11"/>
@@ -61623,11 +61620,11 @@
       </c>
       <c r="N108" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O108" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P108">
         <f t="shared" si="11"/>
@@ -61670,11 +61667,11 @@
       </c>
       <c r="N109" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O109" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P109">
         <f t="shared" si="11"/>
@@ -61717,11 +61714,11 @@
       </c>
       <c r="N110" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O110" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P110">
         <f t="shared" si="11"/>
@@ -61767,11 +61764,11 @@
       </c>
       <c r="N111" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O111" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P111">
         <f t="shared" si="11"/>
@@ -61817,11 +61814,11 @@
       </c>
       <c r="N112" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O112" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P112">
         <f t="shared" si="11"/>
@@ -61867,11 +61864,11 @@
       </c>
       <c r="N113" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O113" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P113">
         <f t="shared" si="11"/>
@@ -61917,11 +61914,11 @@
       </c>
       <c r="N114" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O114" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P114">
         <f t="shared" si="11"/>
@@ -61967,11 +61964,11 @@
       </c>
       <c r="N115" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O115" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P115">
         <f t="shared" si="11"/>
@@ -62017,11 +62014,11 @@
       </c>
       <c r="N116" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O116" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P116">
         <f t="shared" si="11"/>
@@ -62067,11 +62064,11 @@
       </c>
       <c r="N117" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O117" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P117">
         <f t="shared" si="11"/>
@@ -62117,11 +62114,11 @@
       </c>
       <c r="N118" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O118" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P118">
         <f t="shared" si="11"/>
@@ -62167,11 +62164,11 @@
       </c>
       <c r="N119" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O119" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P119">
         <f t="shared" si="11"/>
@@ -62217,11 +62214,11 @@
       </c>
       <c r="N120" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O120" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P120">
         <f t="shared" si="11"/>
@@ -62267,11 +62264,11 @@
       </c>
       <c r="N121" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O121" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P121">
         <f t="shared" si="11"/>
@@ -62317,11 +62314,11 @@
       </c>
       <c r="N122" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O122" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P122">
         <f t="shared" si="11"/>
@@ -62367,11 +62364,11 @@
       </c>
       <c r="N123" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O123" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P123">
         <f t="shared" si="11"/>
@@ -62417,11 +62414,11 @@
       </c>
       <c r="N124" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O124" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P124">
         <f t="shared" si="11"/>
@@ -62467,11 +62464,11 @@
       </c>
       <c r="N125" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O125" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P125">
         <f t="shared" si="11"/>
@@ -62517,11 +62514,11 @@
       </c>
       <c r="N126" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O126" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P126">
         <f t="shared" si="11"/>
@@ -62567,11 +62564,11 @@
       </c>
       <c r="N127" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O127" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P127">
         <f t="shared" si="11"/>
@@ -62617,11 +62614,11 @@
       </c>
       <c r="N128" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O128" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P128">
         <f t="shared" si="11"/>
@@ -62667,11 +62664,11 @@
       </c>
       <c r="N129" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O129" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P129">
         <f t="shared" si="11"/>
@@ -62717,11 +62714,11 @@
       </c>
       <c r="N130" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O130" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P130">
         <f t="shared" si="11"/>
@@ -62767,11 +62764,11 @@
       </c>
       <c r="N131" t="b">
         <f t="shared" ref="N131:N194" si="16">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;2,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),201,100)),G131)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O131" t="b">
         <f t="shared" ref="O131:O194" si="17">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;3,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),301,100)),G131)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P131">
         <f t="shared" ref="P131:P194" si="18">L131*M131*N131*O131</f>
@@ -62817,11 +62814,11 @@
       </c>
       <c r="N132" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O132" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P132">
         <f t="shared" si="18"/>
@@ -62867,11 +62864,11 @@
       </c>
       <c r="N133" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O133" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P133">
         <f t="shared" si="18"/>
@@ -62917,11 +62914,11 @@
       </c>
       <c r="N134" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O134" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P134">
         <f t="shared" si="18"/>
@@ -62967,11 +62964,11 @@
       </c>
       <c r="N135" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O135" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P135">
         <f t="shared" si="18"/>
@@ -63017,11 +63014,11 @@
       </c>
       <c r="N136" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O136" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P136">
         <f t="shared" si="18"/>
@@ -63067,11 +63064,11 @@
       </c>
       <c r="N137" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O137" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P137">
         <f t="shared" si="18"/>
@@ -63117,11 +63114,11 @@
       </c>
       <c r="N138" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O138" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P138">
         <f t="shared" si="18"/>
@@ -63167,11 +63164,11 @@
       </c>
       <c r="N139" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O139" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P139">
         <f t="shared" si="18"/>
@@ -63217,11 +63214,11 @@
       </c>
       <c r="N140" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O140" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P140">
         <f t="shared" si="18"/>
@@ -63264,11 +63261,11 @@
       </c>
       <c r="N141" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O141" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P141">
         <f t="shared" si="18"/>
@@ -63311,11 +63308,11 @@
       </c>
       <c r="N142" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O142" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P142">
         <f t="shared" si="18"/>
@@ -63361,11 +63358,11 @@
       </c>
       <c r="N143" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O143" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P143">
         <f t="shared" si="18"/>
@@ -63408,11 +63405,11 @@
       </c>
       <c r="N144" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O144" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P144">
         <f t="shared" si="18"/>
@@ -63458,11 +63455,11 @@
       </c>
       <c r="N145" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O145" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P145">
         <f t="shared" si="18"/>
@@ -63504,15 +63501,15 @@
       </c>
       <c r="M146" t="b">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N146" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O146" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P146">
         <f t="shared" si="18"/>
@@ -63554,15 +63551,15 @@
       </c>
       <c r="M147" t="b">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N147" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O147" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P147">
         <f t="shared" si="18"/>
@@ -63604,15 +63601,15 @@
       </c>
       <c r="M148" t="b">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N148" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O148" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P148">
         <f t="shared" si="18"/>
@@ -63654,15 +63651,15 @@
       </c>
       <c r="M149" t="b">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N149" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O149" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P149">
         <f t="shared" si="18"/>
@@ -63704,15 +63701,15 @@
       </c>
       <c r="M150" t="b">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N150" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O150" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P150">
         <f t="shared" si="18"/>
@@ -63754,15 +63751,15 @@
       </c>
       <c r="M151" t="b">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N151" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O151" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P151">
         <f t="shared" si="18"/>
@@ -63804,15 +63801,15 @@
       </c>
       <c r="M152" t="b">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N152" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O152" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P152">
         <f t="shared" si="18"/>
@@ -63858,11 +63855,11 @@
       </c>
       <c r="N153" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O153" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P153">
         <f t="shared" si="18"/>
@@ -63908,11 +63905,11 @@
       </c>
       <c r="N154" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O154" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P154">
         <f t="shared" si="18"/>
@@ -63958,11 +63955,11 @@
       </c>
       <c r="N155" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O155" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P155">
         <f t="shared" si="18"/>
@@ -64008,11 +64005,11 @@
       </c>
       <c r="N156" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O156" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P156">
         <f t="shared" si="18"/>
@@ -64051,15 +64048,15 @@
       </c>
       <c r="M157" t="b">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N157" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O157" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P157">
         <f t="shared" si="18"/>
@@ -64102,11 +64099,11 @@
       </c>
       <c r="N158" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O158" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P158">
         <f t="shared" si="18"/>
@@ -64149,11 +64146,11 @@
       </c>
       <c r="N159" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O159" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P159">
         <f t="shared" si="18"/>
@@ -64196,11 +64193,11 @@
       </c>
       <c r="N160" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O160" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P160">
         <f t="shared" si="18"/>
@@ -64243,11 +64240,11 @@
       </c>
       <c r="N161" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O161" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P161">
         <f t="shared" si="18"/>
@@ -64290,11 +64287,11 @@
       </c>
       <c r="N162" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O162" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P162">
         <f t="shared" si="18"/>
@@ -64337,11 +64334,11 @@
       </c>
       <c r="N163" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O163" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P163">
         <f t="shared" si="18"/>
@@ -64384,11 +64381,11 @@
       </c>
       <c r="N164" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O164" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P164">
         <f t="shared" si="18"/>
@@ -64431,11 +64428,11 @@
       </c>
       <c r="N165" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O165" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P165">
         <f t="shared" si="18"/>
@@ -64478,11 +64475,11 @@
       </c>
       <c r="N166" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O166" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P166">
         <f t="shared" si="18"/>
@@ -64528,11 +64525,11 @@
       </c>
       <c r="N167" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O167" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P167">
         <f t="shared" si="18"/>
@@ -64578,11 +64575,11 @@
       </c>
       <c r="N168" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O168" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P168">
         <f t="shared" si="18"/>
@@ -64628,11 +64625,11 @@
       </c>
       <c r="N169" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O169" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P169">
         <f t="shared" si="18"/>
@@ -64678,11 +64675,11 @@
       </c>
       <c r="N170" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O170" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P170">
         <f t="shared" si="18"/>
@@ -64724,15 +64721,15 @@
       </c>
       <c r="M171" t="b">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N171" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O171" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P171">
         <f t="shared" si="18"/>
@@ -64778,11 +64775,11 @@
       </c>
       <c r="N172" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O172" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P172">
         <f t="shared" si="18"/>
@@ -64828,11 +64825,11 @@
       </c>
       <c r="N173" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O173" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P173">
         <f t="shared" si="18"/>
@@ -64878,11 +64875,11 @@
       </c>
       <c r="N174" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O174" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P174">
         <f t="shared" si="18"/>
@@ -64925,11 +64922,11 @@
       </c>
       <c r="N175" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O175" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P175">
         <f t="shared" si="18"/>
@@ -64975,11 +64972,11 @@
       </c>
       <c r="N176" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O176" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P176">
         <f t="shared" si="18"/>
@@ -65022,11 +65019,11 @@
       </c>
       <c r="N177" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O177" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P177">
         <f t="shared" si="18"/>
@@ -65068,15 +65065,15 @@
       </c>
       <c r="M178" t="b">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N178" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O178" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P178">
         <f t="shared" si="18"/>
@@ -65118,15 +65115,15 @@
       </c>
       <c r="M179" t="b">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N179" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O179" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P179">
         <f t="shared" si="18"/>
@@ -65168,15 +65165,15 @@
       </c>
       <c r="M180" t="b">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N180" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O180" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P180">
         <f t="shared" si="18"/>
@@ -65218,15 +65215,15 @@
       </c>
       <c r="M181" t="b">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N181" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O181" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P181">
         <f t="shared" si="18"/>
@@ -65268,15 +65265,15 @@
       </c>
       <c r="M182" t="b">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N182" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O182" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P182">
         <f t="shared" si="18"/>
@@ -65322,11 +65319,11 @@
       </c>
       <c r="N183" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O183" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P183">
         <f t="shared" si="18"/>
@@ -65372,11 +65369,11 @@
       </c>
       <c r="N184" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O184" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P184">
         <f t="shared" si="18"/>
@@ -65419,11 +65416,11 @@
       </c>
       <c r="N185" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O185" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P185">
         <f t="shared" si="18"/>
@@ -65466,11 +65463,11 @@
       </c>
       <c r="N186" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O186" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P186">
         <f t="shared" si="18"/>
@@ -65516,11 +65513,11 @@
       </c>
       <c r="N187" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O187" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P187">
         <f t="shared" si="18"/>
@@ -65566,11 +65563,11 @@
       </c>
       <c r="N188" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O188" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P188">
         <f t="shared" si="18"/>
@@ -65616,11 +65613,11 @@
       </c>
       <c r="N189" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O189" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P189">
         <f t="shared" si="18"/>
@@ -65663,11 +65660,11 @@
       </c>
       <c r="N190" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O190" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P190">
         <f t="shared" si="18"/>
@@ -65713,11 +65710,11 @@
       </c>
       <c r="N191" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O191" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P191">
         <f t="shared" si="18"/>
@@ -65760,11 +65757,11 @@
       </c>
       <c r="N192" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O192" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P192">
         <f t="shared" si="18"/>
@@ -65803,15 +65800,15 @@
       </c>
       <c r="M193" t="b">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N193" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O193" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P193">
         <f t="shared" si="18"/>
@@ -65850,15 +65847,15 @@
       </c>
       <c r="M194" t="b">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N194" t="b">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O194" t="b">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P194">
         <f t="shared" si="18"/>
@@ -65904,11 +65901,11 @@
       </c>
       <c r="N195" t="b">
         <f t="shared" ref="N195:N258" si="23">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;2,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),201,100)),G195)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O195" t="b">
         <f t="shared" ref="O195:O258" si="24">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;3,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),301,100)),G195)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P195">
         <f t="shared" ref="P195:P258" si="25">L195*M195*N195*O195</f>
@@ -65954,11 +65951,11 @@
       </c>
       <c r="N196" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O196" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P196">
         <f t="shared" si="25"/>
@@ -65997,15 +65994,15 @@
       </c>
       <c r="M197" t="b">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N197" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O197" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P197">
         <f t="shared" si="25"/>
@@ -66044,15 +66041,15 @@
       </c>
       <c r="M198" t="b">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N198" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O198" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P198">
         <f t="shared" si="25"/>
@@ -66091,15 +66088,15 @@
       </c>
       <c r="M199" t="b">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N199" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O199" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P199">
         <f t="shared" si="25"/>
@@ -66142,11 +66139,11 @@
       </c>
       <c r="N200" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O200" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P200">
         <f t="shared" si="25"/>
@@ -66189,11 +66186,11 @@
       </c>
       <c r="N201" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O201" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P201">
         <f t="shared" si="25"/>
@@ -66236,11 +66233,11 @@
       </c>
       <c r="N202" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O202" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P202">
         <f t="shared" si="25"/>
@@ -66283,11 +66280,11 @@
       </c>
       <c r="N203" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O203" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P203">
         <f t="shared" si="25"/>
@@ -66330,11 +66327,11 @@
       </c>
       <c r="N204" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O204" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P204">
         <f t="shared" si="25"/>
@@ -66377,11 +66374,11 @@
       </c>
       <c r="N205" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O205" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P205">
         <f t="shared" si="25"/>
@@ -66420,15 +66417,15 @@
       </c>
       <c r="M206" t="b">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N206" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O206" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P206">
         <f t="shared" si="25"/>
@@ -66471,11 +66468,11 @@
       </c>
       <c r="N207" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O207" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P207">
         <f t="shared" si="25"/>
@@ -66518,11 +66515,11 @@
       </c>
       <c r="N208" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O208" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P208">
         <f t="shared" si="25"/>
@@ -66565,11 +66562,11 @@
       </c>
       <c r="N209" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O209" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P209">
         <f t="shared" si="25"/>
@@ -66612,11 +66609,11 @@
       </c>
       <c r="N210" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O210" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P210">
         <f t="shared" si="25"/>
@@ -66659,11 +66656,11 @@
       </c>
       <c r="N211" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O211" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P211">
         <f t="shared" si="25"/>
@@ -66706,11 +66703,11 @@
       </c>
       <c r="N212" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O212" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P212">
         <f t="shared" si="25"/>
@@ -66753,11 +66750,11 @@
       </c>
       <c r="N213" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O213" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P213">
         <f t="shared" si="25"/>
@@ -66800,11 +66797,11 @@
       </c>
       <c r="N214" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O214" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P214">
         <f t="shared" si="25"/>
@@ -66847,11 +66844,11 @@
       </c>
       <c r="N215" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O215" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P215">
         <f t="shared" si="25"/>
@@ -66894,11 +66891,11 @@
       </c>
       <c r="N216" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O216" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P216">
         <f t="shared" si="25"/>
@@ -66941,11 +66938,11 @@
       </c>
       <c r="N217" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O217" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P217">
         <f t="shared" si="25"/>
@@ -66988,11 +66985,11 @@
       </c>
       <c r="N218" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O218" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P218">
         <f t="shared" si="25"/>
@@ -67035,11 +67032,11 @@
       </c>
       <c r="N219" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O219" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P219">
         <f t="shared" si="25"/>
@@ -67085,11 +67082,11 @@
       </c>
       <c r="N220" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O220" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P220">
         <f t="shared" si="25"/>
@@ -67132,11 +67129,11 @@
       </c>
       <c r="N221" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O221" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P221">
         <f t="shared" si="25"/>
@@ -67182,11 +67179,11 @@
       </c>
       <c r="N222" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O222" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P222">
         <f t="shared" si="25"/>
@@ -67229,11 +67226,11 @@
       </c>
       <c r="N223" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O223" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P223">
         <f t="shared" si="25"/>
@@ -67276,11 +67273,11 @@
       </c>
       <c r="N224" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O224" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P224">
         <f t="shared" si="25"/>
@@ -67323,11 +67320,11 @@
       </c>
       <c r="N225" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O225" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P225">
         <f t="shared" si="25"/>
@@ -67370,11 +67367,11 @@
       </c>
       <c r="N226" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O226" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P226">
         <f t="shared" si="25"/>
@@ -67417,11 +67414,11 @@
       </c>
       <c r="N227" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O227" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P227">
         <f t="shared" si="25"/>
@@ -67464,11 +67461,11 @@
       </c>
       <c r="N228" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O228" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P228">
         <f t="shared" si="25"/>
@@ -67511,11 +67508,11 @@
       </c>
       <c r="N229" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O229" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P229">
         <f t="shared" si="25"/>
@@ -67558,11 +67555,11 @@
       </c>
       <c r="N230" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O230" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P230">
         <f t="shared" si="25"/>
@@ -67605,11 +67602,11 @@
       </c>
       <c r="N231" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O231" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P231">
         <f t="shared" si="25"/>
@@ -67648,15 +67645,15 @@
       </c>
       <c r="M232" t="b">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N232" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O232" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P232">
         <f t="shared" si="25"/>
@@ -67699,11 +67696,11 @@
       </c>
       <c r="N233" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O233" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P233">
         <f t="shared" si="25"/>
@@ -67746,11 +67743,11 @@
       </c>
       <c r="N234" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O234" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P234">
         <f t="shared" si="25"/>
@@ -67793,11 +67790,11 @@
       </c>
       <c r="N235" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O235" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P235">
         <f t="shared" si="25"/>
@@ -67840,11 +67837,11 @@
       </c>
       <c r="N236" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O236" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P236">
         <f t="shared" si="25"/>
@@ -67887,11 +67884,11 @@
       </c>
       <c r="N237" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O237" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P237">
         <f t="shared" si="25"/>
@@ -67934,11 +67931,11 @@
       </c>
       <c r="N238" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O238" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P238">
         <f t="shared" si="25"/>
@@ -67981,11 +67978,11 @@
       </c>
       <c r="N239" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O239" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P239">
         <f t="shared" si="25"/>
@@ -68028,11 +68025,11 @@
       </c>
       <c r="N240" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O240" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P240">
         <f t="shared" si="25"/>
@@ -68075,11 +68072,11 @@
       </c>
       <c r="N241" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O241" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P241">
         <f t="shared" si="25"/>
@@ -68122,11 +68119,11 @@
       </c>
       <c r="N242" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O242" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P242">
         <f t="shared" si="25"/>
@@ -68169,11 +68166,11 @@
       </c>
       <c r="N243" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O243" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P243">
         <f t="shared" si="25"/>
@@ -68216,11 +68213,11 @@
       </c>
       <c r="N244" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O244" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P244">
         <f t="shared" si="25"/>
@@ -68263,11 +68260,11 @@
       </c>
       <c r="N245" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O245" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P245">
         <f t="shared" si="25"/>
@@ -68313,11 +68310,11 @@
       </c>
       <c r="N246" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O246" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P246">
         <f t="shared" si="25"/>
@@ -68360,11 +68357,11 @@
       </c>
       <c r="N247" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O247" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P247">
         <f t="shared" si="25"/>
@@ -68403,15 +68400,15 @@
       </c>
       <c r="M248" t="b">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N248" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O248" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P248">
         <f t="shared" si="25"/>
@@ -68454,11 +68451,11 @@
       </c>
       <c r="N249" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O249" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P249">
         <f t="shared" si="25"/>
@@ -68501,11 +68498,11 @@
       </c>
       <c r="N250" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O250" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P250">
         <f t="shared" si="25"/>
@@ -68548,11 +68545,11 @@
       </c>
       <c r="N251" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O251" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P251">
         <f t="shared" si="25"/>
@@ -68595,11 +68592,11 @@
       </c>
       <c r="N252" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O252" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P252">
         <f t="shared" si="25"/>
@@ -68642,11 +68639,11 @@
       </c>
       <c r="N253" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O253" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P253">
         <f t="shared" si="25"/>
@@ -68689,11 +68686,11 @@
       </c>
       <c r="N254" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O254" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P254">
         <f t="shared" si="25"/>
@@ -68736,11 +68733,11 @@
       </c>
       <c r="N255" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O255" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P255">
         <f t="shared" si="25"/>
@@ -68783,11 +68780,11 @@
       </c>
       <c r="N256" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O256" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P256">
         <f t="shared" si="25"/>
@@ -68830,11 +68827,11 @@
       </c>
       <c r="N257" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O257" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P257">
         <f t="shared" si="25"/>
@@ -68877,11 +68874,11 @@
       </c>
       <c r="N258" t="b">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O258" t="b">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P258">
         <f t="shared" si="25"/>
@@ -68924,11 +68921,11 @@
       </c>
       <c r="N259" t="b">
         <f t="shared" ref="N259:N322" si="30">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;2,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),201,100)),G259)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O259" t="b">
         <f t="shared" ref="O259:O322" si="31">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;3,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),301,100)),G259)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P259">
         <f t="shared" ref="P259:P322" si="32">L259*M259*N259*O259</f>
@@ -68971,11 +68968,11 @@
       </c>
       <c r="N260" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O260" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P260">
         <f t="shared" si="32"/>
@@ -69018,11 +69015,11 @@
       </c>
       <c r="N261" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O261" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P261">
         <f t="shared" si="32"/>
@@ -69057,23 +69054,23 @@
       </c>
       <c r="L262" t="b">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M262" t="b">
         <f t="shared" si="29"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N262" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O262" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P262">
         <f t="shared" si="32"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q262" t="b">
         <f t="shared" si="33"/>
@@ -69081,7 +69078,7 @@
       </c>
       <c r="R262">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:18" ht="19.5" x14ac:dyDescent="0.55000000000000004">
@@ -69108,15 +69105,15 @@
       </c>
       <c r="M263" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N263" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O263" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P263">
         <f t="shared" si="32"/>
@@ -69155,15 +69152,15 @@
       </c>
       <c r="M264" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N264" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O264" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P264">
         <f t="shared" si="32"/>
@@ -69206,11 +69203,11 @@
       </c>
       <c r="N265" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O265" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P265">
         <f t="shared" si="32"/>
@@ -69253,11 +69250,11 @@
       </c>
       <c r="N266" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O266" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P266">
         <f t="shared" si="32"/>
@@ -69300,11 +69297,11 @@
       </c>
       <c r="N267" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O267" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P267">
         <f t="shared" si="32"/>
@@ -69347,11 +69344,11 @@
       </c>
       <c r="N268" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O268" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P268">
         <f t="shared" si="32"/>
@@ -69394,11 +69391,11 @@
       </c>
       <c r="N269" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O269" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P269">
         <f t="shared" si="32"/>
@@ -69441,11 +69438,11 @@
       </c>
       <c r="N270" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O270" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P270">
         <f t="shared" si="32"/>
@@ -69488,11 +69485,11 @@
       </c>
       <c r="N271" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O271" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P271">
         <f t="shared" si="32"/>
@@ -69535,11 +69532,11 @@
       </c>
       <c r="N272" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O272" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P272">
         <f t="shared" si="32"/>
@@ -69582,11 +69579,11 @@
       </c>
       <c r="N273" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O273" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P273">
         <f t="shared" si="32"/>
@@ -69625,15 +69622,15 @@
       </c>
       <c r="M274" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N274" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O274" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P274">
         <f t="shared" si="32"/>
@@ -69672,15 +69669,15 @@
       </c>
       <c r="M275" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N275" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O275" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P275">
         <f t="shared" si="32"/>
@@ -69723,11 +69720,11 @@
       </c>
       <c r="N276" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O276" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P276">
         <f t="shared" si="32"/>
@@ -69770,11 +69767,11 @@
       </c>
       <c r="N277" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O277" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P277">
         <f t="shared" si="32"/>
@@ -69817,11 +69814,11 @@
       </c>
       <c r="N278" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O278" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P278">
         <f t="shared" si="32"/>
@@ -69856,7 +69853,7 @@
       </c>
       <c r="L279" t="b">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M279" t="b">
         <f t="shared" si="29"/>
@@ -69864,11 +69861,11 @@
       </c>
       <c r="N279" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O279" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P279">
         <f t="shared" si="32"/>
@@ -69903,7 +69900,7 @@
       </c>
       <c r="L280" t="b">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M280" t="b">
         <f t="shared" si="29"/>
@@ -69911,11 +69908,11 @@
       </c>
       <c r="N280" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O280" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P280">
         <f t="shared" si="32"/>
@@ -69958,11 +69955,11 @@
       </c>
       <c r="N281" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O281" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P281">
         <f t="shared" si="32"/>
@@ -70005,11 +70002,11 @@
       </c>
       <c r="N282" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O282" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P282">
         <f t="shared" si="32"/>
@@ -70052,11 +70049,11 @@
       </c>
       <c r="N283" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O283" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P283">
         <f t="shared" si="32"/>
@@ -70099,11 +70096,11 @@
       </c>
       <c r="N284" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O284" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P284">
         <f t="shared" si="32"/>
@@ -70145,15 +70142,15 @@
       </c>
       <c r="M285" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N285" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O285" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P285">
         <f t="shared" si="32"/>
@@ -70199,11 +70196,11 @@
       </c>
       <c r="N286" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O286" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P286">
         <f t="shared" si="32"/>
@@ -70245,15 +70242,15 @@
       </c>
       <c r="M287" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N287" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O287" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P287">
         <f t="shared" si="32"/>
@@ -70296,11 +70293,11 @@
       </c>
       <c r="N288" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O288" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P288">
         <f t="shared" si="32"/>
@@ -70343,11 +70340,11 @@
       </c>
       <c r="N289" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O289" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P289">
         <f t="shared" si="32"/>
@@ -70390,11 +70387,11 @@
       </c>
       <c r="N290" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O290" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P290">
         <f t="shared" si="32"/>
@@ -70437,11 +70434,11 @@
       </c>
       <c r="N291" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O291" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P291">
         <f t="shared" si="32"/>
@@ -70484,11 +70481,11 @@
       </c>
       <c r="N292" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O292" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P292">
         <f t="shared" si="32"/>
@@ -70531,11 +70528,11 @@
       </c>
       <c r="N293" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O293" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P293">
         <f t="shared" si="32"/>
@@ -70578,11 +70575,11 @@
       </c>
       <c r="N294" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O294" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P294">
         <f t="shared" si="32"/>
@@ -70625,11 +70622,11 @@
       </c>
       <c r="N295" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O295" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P295">
         <f t="shared" si="32"/>
@@ -70672,11 +70669,11 @@
       </c>
       <c r="N296" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O296" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P296">
         <f t="shared" si="32"/>
@@ -70718,15 +70715,15 @@
       </c>
       <c r="M297" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N297" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O297" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P297">
         <f t="shared" si="32"/>
@@ -70768,15 +70765,15 @@
       </c>
       <c r="M298" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N298" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O298" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P298">
         <f t="shared" si="32"/>
@@ -70818,15 +70815,15 @@
       </c>
       <c r="M299" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N299" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O299" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P299">
         <f t="shared" si="32"/>
@@ -70868,15 +70865,15 @@
       </c>
       <c r="M300" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N300" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O300" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P300">
         <f t="shared" si="32"/>
@@ -70918,15 +70915,15 @@
       </c>
       <c r="M301" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N301" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O301" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P301">
         <f t="shared" si="32"/>
@@ -70969,11 +70966,11 @@
       </c>
       <c r="N302" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O302" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P302">
         <f t="shared" si="32"/>
@@ -71016,11 +71013,11 @@
       </c>
       <c r="N303" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O303" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P303">
         <f t="shared" si="32"/>
@@ -71063,11 +71060,11 @@
       </c>
       <c r="N304" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O304" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P304">
         <f t="shared" si="32"/>
@@ -71113,11 +71110,11 @@
       </c>
       <c r="N305" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O305" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P305">
         <f t="shared" si="32"/>
@@ -71163,11 +71160,11 @@
       </c>
       <c r="N306" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O306" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P306">
         <f t="shared" si="32"/>
@@ -71209,15 +71206,15 @@
       </c>
       <c r="M307" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N307" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O307" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P307">
         <f t="shared" si="32"/>
@@ -71259,15 +71256,15 @@
       </c>
       <c r="M308" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N308" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O308" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P308">
         <f t="shared" si="32"/>
@@ -71309,15 +71306,15 @@
       </c>
       <c r="M309" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N309" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O309" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P309">
         <f t="shared" si="32"/>
@@ -71359,15 +71356,15 @@
       </c>
       <c r="M310" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N310" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O310" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P310">
         <f t="shared" si="32"/>
@@ -71409,15 +71406,15 @@
       </c>
       <c r="M311" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N311" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O311" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P311">
         <f t="shared" si="32"/>
@@ -71463,11 +71460,11 @@
       </c>
       <c r="N312" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O312" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P312">
         <f t="shared" si="32"/>
@@ -71509,15 +71506,15 @@
       </c>
       <c r="M313" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N313" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O313" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P313">
         <f t="shared" si="32"/>
@@ -71559,15 +71556,15 @@
       </c>
       <c r="M314" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N314" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O314" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P314">
         <f t="shared" si="32"/>
@@ -71613,11 +71610,11 @@
       </c>
       <c r="N315" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O315" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P315">
         <f t="shared" si="32"/>
@@ -71660,11 +71657,11 @@
       </c>
       <c r="N316" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O316" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P316">
         <f t="shared" si="32"/>
@@ -71707,11 +71704,11 @@
       </c>
       <c r="N317" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O317" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P317">
         <f t="shared" si="32"/>
@@ -71750,15 +71747,15 @@
       </c>
       <c r="M318" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N318" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O318" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P318">
         <f t="shared" si="32"/>
@@ -71797,15 +71794,15 @@
       </c>
       <c r="M319" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N319" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O319" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P319">
         <f t="shared" si="32"/>
@@ -71844,15 +71841,15 @@
       </c>
       <c r="M320" t="b">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N320" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O320" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P320">
         <f t="shared" si="32"/>
@@ -71895,11 +71892,11 @@
       </c>
       <c r="N321" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O321" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P321">
         <f t="shared" si="32"/>
@@ -71942,11 +71939,11 @@
       </c>
       <c r="N322" t="b">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O322" t="b">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P322">
         <f t="shared" si="32"/>
@@ -71985,15 +71982,15 @@
       </c>
       <c r="M323" t="b">
         <f t="shared" ref="M323:M386" si="36">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;1,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),101,100)),G323)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N323" t="b">
         <f t="shared" ref="N323:N386" si="37">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;2,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),201,100)),G323)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O323" t="b">
         <f t="shared" ref="O323:O386" si="38">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;3,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),301,100)),G323)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P323">
         <f t="shared" ref="P323:P386" si="39">L323*M323*N323*O323</f>
@@ -72032,15 +72029,15 @@
       </c>
       <c r="M324" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N324" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O324" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P324">
         <f t="shared" si="39"/>
@@ -72079,15 +72076,15 @@
       </c>
       <c r="M325" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N325" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O325" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P325">
         <f t="shared" si="39"/>
@@ -72126,15 +72123,15 @@
       </c>
       <c r="M326" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N326" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O326" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P326">
         <f t="shared" si="39"/>
@@ -72173,15 +72170,15 @@
       </c>
       <c r="M327" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N327" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O327" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P327">
         <f t="shared" si="39"/>
@@ -72224,11 +72221,11 @@
       </c>
       <c r="N328" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O328" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P328">
         <f t="shared" si="39"/>
@@ -72271,11 +72268,11 @@
       </c>
       <c r="N329" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O329" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P329">
         <f t="shared" si="39"/>
@@ -72318,11 +72315,11 @@
       </c>
       <c r="N330" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O330" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P330">
         <f t="shared" si="39"/>
@@ -72365,11 +72362,11 @@
       </c>
       <c r="N331" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O331" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P331">
         <f t="shared" si="39"/>
@@ -72412,11 +72409,11 @@
       </c>
       <c r="N332" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O332" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P332">
         <f t="shared" si="39"/>
@@ -72459,11 +72456,11 @@
       </c>
       <c r="N333" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O333" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P333">
         <f t="shared" si="39"/>
@@ -72502,15 +72499,15 @@
       </c>
       <c r="M334" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N334" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O334" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P334">
         <f t="shared" si="39"/>
@@ -72553,11 +72550,11 @@
       </c>
       <c r="N335" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O335" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P335">
         <f t="shared" si="39"/>
@@ -72600,11 +72597,11 @@
       </c>
       <c r="N336" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O336" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P336">
         <f t="shared" si="39"/>
@@ -72647,11 +72644,11 @@
       </c>
       <c r="N337" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O337" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P337">
         <f t="shared" si="39"/>
@@ -72694,11 +72691,11 @@
       </c>
       <c r="N338" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O338" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P338">
         <f t="shared" si="39"/>
@@ -72741,11 +72738,11 @@
       </c>
       <c r="N339" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O339" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P339">
         <f t="shared" si="39"/>
@@ -72788,11 +72785,11 @@
       </c>
       <c r="N340" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O340" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P340">
         <f t="shared" si="39"/>
@@ -72835,11 +72832,11 @@
       </c>
       <c r="N341" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O341" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P341">
         <f t="shared" si="39"/>
@@ -72882,11 +72879,11 @@
       </c>
       <c r="N342" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O342" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P342">
         <f t="shared" si="39"/>
@@ -72929,11 +72926,11 @@
       </c>
       <c r="N343" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O343" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P343">
         <f t="shared" si="39"/>
@@ -72976,11 +72973,11 @@
       </c>
       <c r="N344" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O344" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P344">
         <f t="shared" si="39"/>
@@ -73023,11 +73020,11 @@
       </c>
       <c r="N345" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O345" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P345">
         <f t="shared" si="39"/>
@@ -73070,11 +73067,11 @@
       </c>
       <c r="N346" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O346" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P346">
         <f t="shared" si="39"/>
@@ -73117,11 +73114,11 @@
       </c>
       <c r="N347" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O347" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P347">
         <f t="shared" si="39"/>
@@ -73160,15 +73157,15 @@
       </c>
       <c r="M348" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N348" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O348" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P348">
         <f t="shared" si="39"/>
@@ -73211,11 +73208,11 @@
       </c>
       <c r="N349" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O349" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P349">
         <f t="shared" si="39"/>
@@ -73254,15 +73251,15 @@
       </c>
       <c r="M350" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N350" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O350" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P350">
         <f t="shared" si="39"/>
@@ -73305,11 +73302,11 @@
       </c>
       <c r="N351" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O351" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P351">
         <f t="shared" si="39"/>
@@ -73352,11 +73349,11 @@
       </c>
       <c r="N352" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O352" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P352">
         <f t="shared" si="39"/>
@@ -73399,11 +73396,11 @@
       </c>
       <c r="N353" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O353" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P353">
         <f t="shared" si="39"/>
@@ -73446,11 +73443,11 @@
       </c>
       <c r="N354" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O354" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P354">
         <f t="shared" si="39"/>
@@ -73493,11 +73490,11 @@
       </c>
       <c r="N355" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O355" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P355">
         <f t="shared" si="39"/>
@@ -73540,11 +73537,11 @@
       </c>
       <c r="N356" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O356" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P356">
         <f t="shared" si="39"/>
@@ -73587,11 +73584,11 @@
       </c>
       <c r="N357" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O357" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P357">
         <f t="shared" si="39"/>
@@ -73634,11 +73631,11 @@
       </c>
       <c r="N358" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O358" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P358">
         <f t="shared" si="39"/>
@@ -73677,15 +73674,15 @@
       </c>
       <c r="M359" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N359" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O359" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P359">
         <f t="shared" si="39"/>
@@ -73728,11 +73725,11 @@
       </c>
       <c r="N360" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O360" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P360">
         <f t="shared" si="39"/>
@@ -73775,11 +73772,11 @@
       </c>
       <c r="N361" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O361" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P361">
         <f t="shared" si="39"/>
@@ -73822,11 +73819,11 @@
       </c>
       <c r="N362" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O362" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P362">
         <f t="shared" si="39"/>
@@ -73869,11 +73866,11 @@
       </c>
       <c r="N363" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O363" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P363">
         <f t="shared" si="39"/>
@@ -73916,11 +73913,11 @@
       </c>
       <c r="N364" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O364" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P364">
         <f t="shared" si="39"/>
@@ -73963,11 +73960,11 @@
       </c>
       <c r="N365" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O365" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P365">
         <f t="shared" si="39"/>
@@ -74006,15 +74003,15 @@
       </c>
       <c r="M366" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N366" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O366" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P366">
         <f t="shared" si="39"/>
@@ -74053,15 +74050,15 @@
       </c>
       <c r="M367" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N367" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O367" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P367">
         <f t="shared" si="39"/>
@@ -74100,15 +74097,15 @@
       </c>
       <c r="M368" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N368" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O368" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P368">
         <f t="shared" si="39"/>
@@ -74151,11 +74148,11 @@
       </c>
       <c r="N369" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O369" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P369">
         <f t="shared" si="39"/>
@@ -74198,11 +74195,11 @@
       </c>
       <c r="N370" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O370" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P370">
         <f t="shared" si="39"/>
@@ -74245,11 +74242,11 @@
       </c>
       <c r="N371" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O371" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P371">
         <f t="shared" si="39"/>
@@ -74295,11 +74292,11 @@
       </c>
       <c r="N372" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O372" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P372">
         <f t="shared" si="39"/>
@@ -74342,11 +74339,11 @@
       </c>
       <c r="N373" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O373" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P373">
         <f t="shared" si="39"/>
@@ -74388,15 +74385,15 @@
       </c>
       <c r="M374" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N374" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O374" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P374">
         <f t="shared" si="39"/>
@@ -74438,15 +74435,15 @@
       </c>
       <c r="M375" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N375" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O375" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P375">
         <f t="shared" si="39"/>
@@ -74489,11 +74486,11 @@
       </c>
       <c r="N376" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O376" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P376">
         <f t="shared" si="39"/>
@@ -74536,11 +74533,11 @@
       </c>
       <c r="N377" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O377" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P377">
         <f t="shared" si="39"/>
@@ -74583,11 +74580,11 @@
       </c>
       <c r="N378" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O378" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P378">
         <f t="shared" si="39"/>
@@ -74629,15 +74626,15 @@
       </c>
       <c r="M379" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N379" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O379" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P379">
         <f t="shared" si="39"/>
@@ -74679,15 +74676,15 @@
       </c>
       <c r="M380" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N380" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O380" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P380">
         <f t="shared" si="39"/>
@@ -74729,15 +74726,15 @@
       </c>
       <c r="M381" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N381" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O381" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P381">
         <f t="shared" si="39"/>
@@ -74776,15 +74773,15 @@
       </c>
       <c r="M382" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N382" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O382" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P382">
         <f t="shared" si="39"/>
@@ -74823,15 +74820,15 @@
       </c>
       <c r="M383" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N383" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O383" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P383">
         <f t="shared" si="39"/>
@@ -74870,15 +74867,15 @@
       </c>
       <c r="M384" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N384" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O384" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P384">
         <f t="shared" si="39"/>
@@ -74920,15 +74917,15 @@
       </c>
       <c r="M385" t="b">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N385" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O385" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P385">
         <f t="shared" si="39"/>
@@ -74971,11 +74968,11 @@
       </c>
       <c r="N386" t="b">
         <f t="shared" si="37"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O386" t="b">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P386">
         <f t="shared" si="39"/>
@@ -75021,11 +75018,11 @@
       </c>
       <c r="N387" t="b">
         <f t="shared" ref="N387:N450" si="44">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;2,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),201,100)),G387)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O387" t="b">
         <f t="shared" ref="O387:O450" si="45">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;3,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),301,100)),G387)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P387">
         <f t="shared" ref="P387:P450" si="46">L387*M387*N387*O387</f>
@@ -75067,15 +75064,15 @@
       </c>
       <c r="M388" t="b">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N388" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O388" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P388">
         <f t="shared" si="46"/>
@@ -75117,15 +75114,15 @@
       </c>
       <c r="M389" t="b">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N389" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O389" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P389">
         <f t="shared" si="46"/>
@@ -75168,11 +75165,11 @@
       </c>
       <c r="N390" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O390" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P390">
         <f t="shared" si="46"/>
@@ -75215,11 +75212,11 @@
       </c>
       <c r="N391" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O391" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P391">
         <f t="shared" si="46"/>
@@ -75262,11 +75259,11 @@
       </c>
       <c r="N392" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O392" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P392">
         <f t="shared" si="46"/>
@@ -75308,15 +75305,15 @@
       </c>
       <c r="M393" t="b">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N393" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O393" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P393">
         <f t="shared" si="46"/>
@@ -75359,11 +75356,11 @@
       </c>
       <c r="N394" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O394" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P394">
         <f t="shared" si="46"/>
@@ -75406,11 +75403,11 @@
       </c>
       <c r="N395" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O395" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P395">
         <f t="shared" si="46"/>
@@ -75453,11 +75450,11 @@
       </c>
       <c r="N396" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O396" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P396">
         <f t="shared" si="46"/>
@@ -75500,11 +75497,11 @@
       </c>
       <c r="N397" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O397" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P397">
         <f t="shared" si="46"/>
@@ -75550,11 +75547,11 @@
       </c>
       <c r="N398" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O398" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P398">
         <f t="shared" si="46"/>
@@ -75600,11 +75597,11 @@
       </c>
       <c r="N399" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O399" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P399">
         <f t="shared" si="46"/>
@@ -75650,11 +75647,11 @@
       </c>
       <c r="N400" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O400" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P400">
         <f t="shared" si="46"/>
@@ -75700,11 +75697,11 @@
       </c>
       <c r="N401" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O401" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P401">
         <f t="shared" si="46"/>
@@ -75747,11 +75744,11 @@
       </c>
       <c r="N402" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O402" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P402">
         <f t="shared" si="46"/>
@@ -75793,15 +75790,15 @@
       </c>
       <c r="M403" t="b">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N403" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O403" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P403">
         <f t="shared" si="46"/>
@@ -75843,15 +75840,15 @@
       </c>
       <c r="M404" t="b">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N404" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O404" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P404">
         <f t="shared" si="46"/>
@@ -75893,15 +75890,15 @@
       </c>
       <c r="M405" t="b">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N405" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O405" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P405">
         <f t="shared" si="46"/>
@@ -75947,11 +75944,11 @@
       </c>
       <c r="N406" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O406" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P406">
         <f t="shared" si="46"/>
@@ -75994,11 +75991,11 @@
       </c>
       <c r="N407" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O407" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P407">
         <f t="shared" si="46"/>
@@ -76041,11 +76038,11 @@
       </c>
       <c r="N408" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O408" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P408">
         <f t="shared" si="46"/>
@@ -76088,11 +76085,11 @@
       </c>
       <c r="N409" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O409" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P409">
         <f t="shared" si="46"/>
@@ -76131,15 +76128,15 @@
       </c>
       <c r="M410" t="b">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N410" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O410" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P410">
         <f t="shared" si="46"/>
@@ -76178,15 +76175,15 @@
       </c>
       <c r="M411" t="b">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N411" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O411" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P411">
         <f t="shared" si="46"/>
@@ -76229,11 +76226,11 @@
       </c>
       <c r="N412" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O412" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P412">
         <f t="shared" si="46"/>
@@ -76276,11 +76273,11 @@
       </c>
       <c r="N413" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O413" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P413">
         <f t="shared" si="46"/>
@@ -76323,11 +76320,11 @@
       </c>
       <c r="N414" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O414" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P414">
         <f t="shared" si="46"/>
@@ -76370,11 +76367,11 @@
       </c>
       <c r="N415" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O415" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P415">
         <f t="shared" si="46"/>
@@ -76417,11 +76414,11 @@
       </c>
       <c r="N416" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O416" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P416">
         <f t="shared" si="46"/>
@@ -76464,11 +76461,11 @@
       </c>
       <c r="N417" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O417" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P417">
         <f t="shared" si="46"/>
@@ -76511,11 +76508,11 @@
       </c>
       <c r="N418" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O418" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P418">
         <f t="shared" si="46"/>
@@ -76558,11 +76555,11 @@
       </c>
       <c r="N419" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O419" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P419">
         <f t="shared" si="46"/>
@@ -76605,11 +76602,11 @@
       </c>
       <c r="N420" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O420" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P420">
         <f t="shared" si="46"/>
@@ -76655,11 +76652,11 @@
       </c>
       <c r="N421" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O421" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P421">
         <f t="shared" si="46"/>
@@ -76705,11 +76702,11 @@
       </c>
       <c r="N422" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O422" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P422">
         <f t="shared" si="46"/>
@@ -76752,11 +76749,11 @@
       </c>
       <c r="N423" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O423" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P423">
         <f t="shared" si="46"/>
@@ -76802,11 +76799,11 @@
       </c>
       <c r="N424" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O424" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P424">
         <f t="shared" si="46"/>
@@ -76845,15 +76842,15 @@
       </c>
       <c r="M425" t="b">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N425" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O425" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P425">
         <f t="shared" si="46"/>
@@ -76892,15 +76889,15 @@
       </c>
       <c r="M426" t="b">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N426" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O426" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P426">
         <f t="shared" si="46"/>
@@ -76943,11 +76940,11 @@
       </c>
       <c r="N427" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O427" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P427">
         <f t="shared" si="46"/>
@@ -76990,11 +76987,11 @@
       </c>
       <c r="N428" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O428" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P428">
         <f t="shared" si="46"/>
@@ -77037,11 +77034,11 @@
       </c>
       <c r="N429" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O429" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P429">
         <f t="shared" si="46"/>
@@ -77084,11 +77081,11 @@
       </c>
       <c r="N430" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O430" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P430">
         <f t="shared" si="46"/>
@@ -77131,11 +77128,11 @@
       </c>
       <c r="N431" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O431" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P431">
         <f t="shared" si="46"/>
@@ -77178,11 +77175,11 @@
       </c>
       <c r="N432" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O432" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P432">
         <f t="shared" si="46"/>
@@ -77225,11 +77222,11 @@
       </c>
       <c r="N433" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O433" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P433">
         <f t="shared" si="46"/>
@@ -77272,11 +77269,11 @@
       </c>
       <c r="N434" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O434" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P434">
         <f t="shared" si="46"/>
@@ -77319,11 +77316,11 @@
       </c>
       <c r="N435" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O435" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P435">
         <f t="shared" si="46"/>
@@ -77365,15 +77362,15 @@
       </c>
       <c r="M436" t="b">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N436" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O436" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P436">
         <f t="shared" si="46"/>
@@ -77416,11 +77413,11 @@
       </c>
       <c r="N437" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O437" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P437">
         <f t="shared" si="46"/>
@@ -77463,11 +77460,11 @@
       </c>
       <c r="N438" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O438" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P438">
         <f t="shared" si="46"/>
@@ -77510,11 +77507,11 @@
       </c>
       <c r="N439" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O439" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P439">
         <f t="shared" si="46"/>
@@ -77557,11 +77554,11 @@
       </c>
       <c r="N440" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O440" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P440">
         <f t="shared" si="46"/>
@@ -77604,11 +77601,11 @@
       </c>
       <c r="N441" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O441" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P441">
         <f t="shared" si="46"/>
@@ -77651,11 +77648,11 @@
       </c>
       <c r="N442" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O442" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P442">
         <f t="shared" si="46"/>
@@ -77698,11 +77695,11 @@
       </c>
       <c r="N443" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O443" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P443">
         <f t="shared" si="46"/>
@@ -77745,11 +77742,11 @@
       </c>
       <c r="N444" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O444" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P444">
         <f t="shared" si="46"/>
@@ -77792,11 +77789,11 @@
       </c>
       <c r="N445" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O445" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P445">
         <f t="shared" si="46"/>
@@ -77839,11 +77836,11 @@
       </c>
       <c r="N446" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O446" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P446">
         <f t="shared" si="46"/>
@@ -77882,15 +77879,15 @@
       </c>
       <c r="M447" t="b">
         <f t="shared" si="43"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N447" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O447" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P447">
         <f t="shared" si="46"/>
@@ -77933,11 +77930,11 @@
       </c>
       <c r="N448" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O448" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P448">
         <f t="shared" si="46"/>
@@ -77980,11 +77977,11 @@
       </c>
       <c r="N449" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O449" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P449">
         <f t="shared" si="46"/>
@@ -78027,11 +78024,11 @@
       </c>
       <c r="N450" t="b">
         <f t="shared" si="44"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O450" t="b">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P450">
         <f t="shared" si="46"/>
@@ -78073,15 +78070,15 @@
       </c>
       <c r="M451" t="b">
         <f t="shared" ref="M451:M514" si="50">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;1,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),101,100)),G451)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N451" t="b">
         <f t="shared" ref="N451:N514" si="51">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;2,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),201,100)),G451)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O451" t="b">
         <f t="shared" ref="O451:O514" si="52">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;3,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),301,100)),G451)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P451">
         <f t="shared" ref="P451:P514" si="53">L451*M451*N451*O451</f>
@@ -78127,11 +78124,11 @@
       </c>
       <c r="N452" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O452" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P452">
         <f t="shared" si="53"/>
@@ -78173,15 +78170,15 @@
       </c>
       <c r="M453" t="b">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N453" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O453" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P453">
         <f t="shared" si="53"/>
@@ -78227,11 +78224,11 @@
       </c>
       <c r="N454" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O454" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P454">
         <f t="shared" si="53"/>
@@ -78277,11 +78274,11 @@
       </c>
       <c r="N455" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O455" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P455">
         <f t="shared" si="53"/>
@@ -78327,11 +78324,11 @@
       </c>
       <c r="N456" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O456" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P456">
         <f t="shared" si="53"/>
@@ -78373,15 +78370,15 @@
       </c>
       <c r="M457" t="b">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N457" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O457" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P457">
         <f t="shared" si="53"/>
@@ -78423,15 +78420,15 @@
       </c>
       <c r="M458" t="b">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N458" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O458" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P458">
         <f t="shared" si="53"/>
@@ -78477,11 +78474,11 @@
       </c>
       <c r="N459" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O459" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P459">
         <f t="shared" si="53"/>
@@ -78527,11 +78524,11 @@
       </c>
       <c r="N460" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O460" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P460">
         <f t="shared" si="53"/>
@@ -78577,11 +78574,11 @@
       </c>
       <c r="N461" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O461" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P461">
         <f t="shared" si="53"/>
@@ -78627,11 +78624,11 @@
       </c>
       <c r="N462" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O462" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P462">
         <f t="shared" si="53"/>
@@ -78677,11 +78674,11 @@
       </c>
       <c r="N463" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O463" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P463">
         <f t="shared" si="53"/>
@@ -78727,11 +78724,11 @@
       </c>
       <c r="N464" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O464" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P464">
         <f t="shared" si="53"/>
@@ -78777,11 +78774,11 @@
       </c>
       <c r="N465" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O465" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P465">
         <f t="shared" si="53"/>
@@ -78827,11 +78824,11 @@
       </c>
       <c r="N466" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O466" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P466">
         <f t="shared" si="53"/>
@@ -78877,11 +78874,11 @@
       </c>
       <c r="N467" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O467" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P467">
         <f t="shared" si="53"/>
@@ -78927,11 +78924,11 @@
       </c>
       <c r="N468" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O468" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P468">
         <f t="shared" si="53"/>
@@ -78977,11 +78974,11 @@
       </c>
       <c r="N469" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O469" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P469">
         <f t="shared" si="53"/>
@@ -79027,11 +79024,11 @@
       </c>
       <c r="N470" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O470" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P470">
         <f t="shared" si="53"/>
@@ -79077,11 +79074,11 @@
       </c>
       <c r="N471" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O471" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P471">
         <f t="shared" si="53"/>
@@ -79127,11 +79124,11 @@
       </c>
       <c r="N472" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O472" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P472">
         <f t="shared" si="53"/>
@@ -79177,11 +79174,11 @@
       </c>
       <c r="N473" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O473" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P473">
         <f t="shared" si="53"/>
@@ -79227,11 +79224,11 @@
       </c>
       <c r="N474" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O474" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P474">
         <f t="shared" si="53"/>
@@ -79277,11 +79274,11 @@
       </c>
       <c r="N475" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O475" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P475">
         <f t="shared" si="53"/>
@@ -79327,11 +79324,11 @@
       </c>
       <c r="N476" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O476" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P476">
         <f t="shared" si="53"/>
@@ -79377,11 +79374,11 @@
       </c>
       <c r="N477" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O477" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P477">
         <f t="shared" si="53"/>
@@ -79427,11 +79424,11 @@
       </c>
       <c r="N478" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O478" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P478">
         <f t="shared" si="53"/>
@@ -79477,11 +79474,11 @@
       </c>
       <c r="N479" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O479" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P479">
         <f t="shared" si="53"/>
@@ -79527,11 +79524,11 @@
       </c>
       <c r="N480" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O480" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P480">
         <f t="shared" si="53"/>
@@ -79577,11 +79574,11 @@
       </c>
       <c r="N481" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O481" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P481">
         <f t="shared" si="53"/>
@@ -79627,11 +79624,11 @@
       </c>
       <c r="N482" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O482" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P482">
         <f t="shared" si="53"/>
@@ -79677,11 +79674,11 @@
       </c>
       <c r="N483" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O483" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P483">
         <f t="shared" si="53"/>
@@ -79727,11 +79724,11 @@
       </c>
       <c r="N484" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O484" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P484">
         <f t="shared" si="53"/>
@@ -79777,11 +79774,11 @@
       </c>
       <c r="N485" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O485" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P485">
         <f t="shared" si="53"/>
@@ -79827,11 +79824,11 @@
       </c>
       <c r="N486" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O486" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P486">
         <f t="shared" si="53"/>
@@ -79873,15 +79870,15 @@
       </c>
       <c r="M487" t="b">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N487" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O487" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P487">
         <f t="shared" si="53"/>
@@ -79927,11 +79924,11 @@
       </c>
       <c r="N488" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O488" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P488">
         <f t="shared" si="53"/>
@@ -79977,11 +79974,11 @@
       </c>
       <c r="N489" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O489" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P489">
         <f t="shared" si="53"/>
@@ -80024,11 +80021,11 @@
       </c>
       <c r="N490" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O490" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P490">
         <f t="shared" si="53"/>
@@ -80074,11 +80071,11 @@
       </c>
       <c r="N491" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O491" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P491">
         <f t="shared" si="53"/>
@@ -80124,11 +80121,11 @@
       </c>
       <c r="N492" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O492" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P492">
         <f t="shared" si="53"/>
@@ -80174,11 +80171,11 @@
       </c>
       <c r="N493" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O493" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P493">
         <f t="shared" si="53"/>
@@ -80224,11 +80221,11 @@
       </c>
       <c r="N494" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O494" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P494">
         <f t="shared" si="53"/>
@@ -80274,11 +80271,11 @@
       </c>
       <c r="N495" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O495" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P495">
         <f t="shared" si="53"/>
@@ -80321,11 +80318,11 @@
       </c>
       <c r="N496" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O496" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P496">
         <f t="shared" si="53"/>
@@ -80367,15 +80364,15 @@
       </c>
       <c r="M497" t="b">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N497" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O497" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P497">
         <f t="shared" si="53"/>
@@ -80417,15 +80414,15 @@
       </c>
       <c r="M498" t="b">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N498" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O498" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P498">
         <f t="shared" si="53"/>
@@ -80467,15 +80464,15 @@
       </c>
       <c r="M499" t="b">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N499" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O499" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P499">
         <f t="shared" si="53"/>
@@ -80517,15 +80514,15 @@
       </c>
       <c r="M500" t="b">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N500" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O500" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P500">
         <f t="shared" si="53"/>
@@ -80571,11 +80568,11 @@
       </c>
       <c r="N501" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O501" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P501">
         <f t="shared" si="53"/>
@@ -80617,15 +80614,15 @@
       </c>
       <c r="M502" t="b">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N502" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O502" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P502">
         <f t="shared" si="53"/>
@@ -80667,15 +80664,15 @@
       </c>
       <c r="M503" t="b">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N503" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O503" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P503">
         <f t="shared" si="53"/>
@@ -80717,15 +80714,15 @@
       </c>
       <c r="M504" t="b">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N504" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O504" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P504">
         <f t="shared" si="53"/>
@@ -80767,15 +80764,15 @@
       </c>
       <c r="M505" t="b">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N505" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O505" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P505">
         <f t="shared" si="53"/>
@@ -80818,11 +80815,11 @@
       </c>
       <c r="N506" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O506" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P506">
         <f t="shared" si="53"/>
@@ -80864,15 +80861,15 @@
       </c>
       <c r="M507" t="b">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N507" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O507" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P507">
         <f t="shared" si="53"/>
@@ -80914,15 +80911,15 @@
       </c>
       <c r="M508" t="b">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N508" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O508" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P508">
         <f t="shared" si="53"/>
@@ -80965,11 +80962,11 @@
       </c>
       <c r="N509" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O509" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P509">
         <f t="shared" si="53"/>
@@ -81012,11 +81009,11 @@
       </c>
       <c r="N510" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O510" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P510">
         <f t="shared" si="53"/>
@@ -81062,11 +81059,11 @@
       </c>
       <c r="N511" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O511" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P511">
         <f t="shared" si="53"/>
@@ -81112,11 +81109,11 @@
       </c>
       <c r="N512" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O512" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P512">
         <f t="shared" si="53"/>
@@ -81162,11 +81159,11 @@
       </c>
       <c r="N513" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O513" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P513">
         <f t="shared" si="53"/>
@@ -81212,11 +81209,11 @@
       </c>
       <c r="N514" t="b">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O514" t="b">
         <f t="shared" si="52"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P514">
         <f t="shared" si="53"/>
@@ -81262,11 +81259,11 @@
       </c>
       <c r="N515" t="b">
         <f t="shared" ref="N515:N538" si="58">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;2,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),201,100)),G515)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O515" t="b">
         <f t="shared" ref="O515:O538" si="59">IF(LEN(TRIM($B$3))-LEN(SUBSTITUTE(TRIM($B$3)," ",""))&lt;3,TRUE,ISNUMBER(SEARCH(TRIM(MID(SUBSTITUTE($B$3," ",REPT(" ",100)),301,100)),G515)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P515">
         <f t="shared" ref="P515:P538" si="60">L515*M515*N515*O515</f>
@@ -81312,11 +81309,11 @@
       </c>
       <c r="N516" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O516" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P516">
         <f t="shared" si="60"/>
@@ -81362,11 +81359,11 @@
       </c>
       <c r="N517" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O517" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P517">
         <f t="shared" si="60"/>
@@ -81412,11 +81409,11 @@
       </c>
       <c r="N518" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O518" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P518">
         <f t="shared" si="60"/>
@@ -81462,11 +81459,11 @@
       </c>
       <c r="N519" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O519" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P519">
         <f t="shared" si="60"/>
@@ -81512,11 +81509,11 @@
       </c>
       <c r="N520" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O520" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P520">
         <f t="shared" si="60"/>
@@ -81562,11 +81559,11 @@
       </c>
       <c r="N521" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O521" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P521">
         <f t="shared" si="60"/>
@@ -81612,11 +81609,11 @@
       </c>
       <c r="N522" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O522" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P522">
         <f t="shared" si="60"/>
@@ -81662,11 +81659,11 @@
       </c>
       <c r="N523" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O523" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P523">
         <f t="shared" si="60"/>
@@ -81708,15 +81705,15 @@
       </c>
       <c r="M524" t="b">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N524" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O524" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P524">
         <f t="shared" si="60"/>
@@ -81758,15 +81755,15 @@
       </c>
       <c r="M525" t="b">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N525" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O525" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P525">
         <f t="shared" si="60"/>
@@ -81808,15 +81805,15 @@
       </c>
       <c r="M526" t="b">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N526" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O526" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P526">
         <f t="shared" si="60"/>
@@ -81858,15 +81855,15 @@
       </c>
       <c r="M527" t="b">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N527" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O527" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P527">
         <f t="shared" si="60"/>
@@ -81909,11 +81906,11 @@
       </c>
       <c r="N528" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O528" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P528">
         <f t="shared" si="60"/>
@@ -81956,11 +81953,11 @@
       </c>
       <c r="N529" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O529" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P529">
         <f t="shared" si="60"/>
@@ -82006,11 +82003,11 @@
       </c>
       <c r="N530" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O530" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P530">
         <f t="shared" si="60"/>
@@ -82056,11 +82053,11 @@
       </c>
       <c r="N531" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O531" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P531">
         <f t="shared" si="60"/>
@@ -82102,15 +82099,15 @@
       </c>
       <c r="M532" t="b">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N532" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O532" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P532">
         <f t="shared" si="60"/>
@@ -82152,15 +82149,15 @@
       </c>
       <c r="M533" t="b">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N533" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O533" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P533">
         <f t="shared" si="60"/>
@@ -82206,11 +82203,11 @@
       </c>
       <c r="N534" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O534" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P534">
         <f t="shared" si="60"/>
@@ -82252,15 +82249,15 @@
       </c>
       <c r="M535" t="b">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N535" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O535" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P535">
         <f t="shared" si="60"/>
@@ -82306,11 +82303,11 @@
       </c>
       <c r="N536" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O536" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P536">
         <f t="shared" si="60"/>
@@ -82356,11 +82353,11 @@
       </c>
       <c r="N537" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O537" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P537">
         <f t="shared" si="60"/>
@@ -82402,15 +82399,15 @@
       </c>
       <c r="M538" t="b">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N538" t="b">
         <f t="shared" si="58"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O538" t="b">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P538">
         <f t="shared" si="60"/>
@@ -82463,7 +82460,7 @@
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{1548533F-29D7-4083-A7CE-8C028384CFBA}">
       <formula1>$K$1:$K$40</formula1>
     </dataValidation>
